--- a/checklists/Group_D_Week_2_Checklist.xlsx
+++ b/checklists/Group_D_Week_2_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a0eabcb09bfda7/Documents/Masters/2026-H5 - Data Science Project/ZZSC9020-Data-Science-Project-Group-D/checklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{007732C5-FDB5-4CCE-8180-572ECD09DCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF4A8078-AC9D-468A-BFD2-F793CC1FE369}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{007732C5-FDB5-4CCE-8180-572ECD09DCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C042BF2-975F-4959-9B25-C67244C6B1DF}"/>
   <bookViews>
     <workbookView xWindow="1815" yWindow="660" windowWidth="27645" windowHeight="19485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Week 2 Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Week 2 Checklist'!$A$3:$E$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Week 2 Checklist'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Week 2 Checklist'!$A$3:$E$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Week 2 Checklist'!$A$1:$E$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Week 2 Checklist'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="55">
   <si>
     <t>Group D - Week 2 Checklist</t>
   </si>
@@ -123,9 +123,6 @@
     <t>☐ Not marked</t>
   </si>
   <si>
-    <t>To be updated by Anders</t>
-  </si>
-  <si>
     <t>Confirm the primary statistical model and benchmark model</t>
   </si>
   <si>
@@ -169,6 +166,30 @@
   </si>
   <si>
     <t>Bae, Kwon and Song (2022) and Yildiz et al. (2018)</t>
+  </si>
+  <si>
+    <t>Finalise modelling definitions and data requirements</t>
+  </si>
+  <si>
+    <t>Set up modelling notebook structure</t>
+  </si>
+  <si>
+    <t>Fit first simple regression</t>
+  </si>
+  <si>
+    <t>◩ In progress</t>
+  </si>
+  <si>
+    <t>Available in initial_modelling.ipynb</t>
+  </si>
+  <si>
+    <t>Multiple linear regression, with XGBoost as benchmark model</t>
+  </si>
+  <si>
+    <t>Available in modelling_notes.md</t>
+  </si>
+  <si>
+    <t>Initial plan in 'Modelling Planning.md'</t>
   </si>
 </sst>
 </file>
@@ -342,8 +363,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Week2Checklist" displayName="Week2Checklist" ref="A3:E23">
-  <autoFilter ref="A3:E23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Week2Checklist" displayName="Week2Checklist" ref="A3:E25">
+  <autoFilter ref="A3:E25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Team Member"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Role / Focus"/>
@@ -643,7 +664,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -872,13 +893,13 @@
         <v>29</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -889,13 +910,13 @@
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -906,13 +927,13 @@
         <v>29</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -923,13 +944,13 @@
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -940,134 +961,166 @@
         <v>29</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="11" t="s">
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="10" t="s">
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D23">
+  <conditionalFormatting sqref="D4:D25">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>ISNUMBER(SEARCH("Complete",D4))</formula>
     </cfRule>
@@ -1076,7 +1129,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D14:D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D14:D25" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"☐ Not marked,☑ Complete,◩ In progress"</formula1>
     </dataValidation>
   </dataValidations>
